--- a/timetable.xlsx
+++ b/timetable.xlsx
@@ -37,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -51,11 +51,32 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -63,6 +84,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -464,7 +486,7 @@
           <t>報到</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr"/>
+      <c r="C2" s="3" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -528,7 +550,7 @@
           <t>Break</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
+      <c r="C6" s="3" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -575,7 +597,7 @@
           <t>Lunch</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr"/>
+      <c r="C9" s="3" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -622,7 +644,7 @@
           <t>Break</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr"/>
+      <c r="C12" s="3" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
@@ -659,6 +681,12 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B12:C12"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>